--- a/漢字（かんじ）/r.xlsx
+++ b/漢字（かんじ）/r.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ら" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="109">
   <si>
     <t>仮名</t>
   </si>
@@ -133,7 +133,8 @@
     <t>有利｜ゆうり
 不利｜ふり
 利率｜りりつ
-利益｜りえき</t>
+利益｜りえき
+権利｜けんり</t>
   </si>
   <si>
     <t>りつ</t>
@@ -379,7 +380,8 @@
     <t>訓練｜くんれん
 訓練所｜くんれんしょ
 練習｜れんしゅう
-練習問題｜れんしゅうもんだい</t>
+練習問題｜れんしゅうもんだい
+防災訓練｜ぼうさいくんれん</t>
   </si>
   <si>
     <t>れき</t>
@@ -487,6 +489,12 @@
 苦労｜くろう
 労働｜ろうどう
 労働省｜ろうどうしょう</t>
+  </si>
+  <si>
+    <t>浪</t>
+  </si>
+  <si>
+    <t>浪費｜おるひ</t>
   </si>
   <si>
     <t>ろく</t>
@@ -520,7 +528,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -545,13 +553,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1001,148 +1002,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1597,7 +1598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="72" spans="1:7">
+    <row r="2" ht="90" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -1890,7 +1891,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" ht="72" spans="1:3">
+    <row r="3" ht="90" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>70</v>
       </c>
@@ -1992,8 +1993,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="31.4444444444444" customWidth="1"/>
   </cols>
@@ -2053,26 +2054,37 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" ht="70.2" customHeight="1" spans="1:3">
+    <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" ht="72" spans="1:3">
+    <row r="7" ht="70.2" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="8" ht="72" spans="1:3">
+      <c r="A8" s="1" t="s">
         <v>106</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/r.xlsx
+++ b/漢字（かんじ）/r.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ら" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="113">
   <si>
     <t>仮名</t>
   </si>
@@ -412,6 +412,7 @@
   </si>
   <si>
     <t>失礼｜しつれい
+無礼｜ぶれい
 礼儀｜れいぎ</t>
   </si>
   <si>
@@ -429,6 +430,13 @@
 実例｜じつれい
 慣例｜かんれい
 比例｜ひれい</t>
+  </si>
+  <si>
+    <t>励</t>
+  </si>
+  <si>
+    <t>奨励｜しょうれい
+奨励金｜しょうれい</t>
   </si>
   <si>
     <t>令</t>
@@ -495,6 +503,12 @@
   </si>
   <si>
     <t>浪費｜おるひ</t>
+  </si>
+  <si>
+    <t>朗</t>
+  </si>
+  <si>
+    <t>朗読｜ろうどく</t>
   </si>
   <si>
     <t>ろく</t>
@@ -1863,7 +1877,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="30.3333333333333" customWidth="1"/>
@@ -1924,7 +1938,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" ht="36" spans="1:3">
+    <row r="6" ht="54" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>78</v>
       </c>
@@ -1968,21 +1982,32 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" ht="72" spans="1:3">
+    <row r="10" ht="36" spans="1:3">
       <c r="A10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="11" ht="72" spans="1:3">
+      <c r="A11" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="11" ht="18" spans="1:3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" ht="18" spans="1:3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1993,8 +2018,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7" outlineLevelCol="2"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="31.4444444444444" customWidth="1"/>
   </cols>
@@ -2012,79 +2037,90 @@
     </row>
     <row r="2" ht="72" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" ht="144" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" ht="70.2" customHeight="1" spans="1:3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" ht="70.2" customHeight="1" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" ht="72" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" ht="72" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/r.xlsx
+++ b/漢字（かんじ）/r.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ら" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="116">
   <si>
     <t>仮名</t>
   </si>
@@ -137,15 +137,13 @@
 権利｜けんり</t>
   </si>
   <si>
-    <t>りつ</t>
-  </si>
-  <si>
-    <t>率</t>
-  </si>
-  <si>
-    <t>能率｜のうりつ
-利率｜りりつ
-生育率｜せいいくりつ</t>
+    <t>りく</t>
+  </si>
+  <si>
+    <t>陸</t>
+  </si>
+  <si>
+    <t>陸地｜りくち</t>
   </si>
   <si>
     <t>理</t>
@@ -156,6 +154,27 @@
 理工｜りこう
 代理｜だいり
 料理｜りょうり</t>
+  </si>
+  <si>
+    <t>りつ</t>
+  </si>
+  <si>
+    <t>率</t>
+  </si>
+  <si>
+    <t>能率｜のうりつ
+利率｜りりつ
+生育率｜せいいくりつ</t>
+  </si>
+  <si>
+    <t>離</t>
+  </si>
+  <si>
+    <t>離合｜りごう
+離婚｜りこん
+離合集散｜りごうしゅうさん
+離散数学｜りさんすうがく
+距離｜きょり</t>
   </si>
   <si>
     <t>立</t>
@@ -170,38 +189,16 @@
 独立行政｜どくりつぎょうせい</t>
   </si>
   <si>
-    <t>離</t>
-  </si>
-  <si>
-    <t>離合｜りごう
-離婚｜りこん
-離合集散｜りごうしゅうさん
-離散数学｜りさんすうがく
-距離｜きょり</t>
+    <t>履</t>
+  </si>
+  <si>
+    <t>履歴｜りれき</t>
   </si>
   <si>
     <t>律</t>
   </si>
   <si>
     <t>因果律｜いんがりつ</t>
-  </si>
-  <si>
-    <t>履</t>
-  </si>
-  <si>
-    <t>履歴｜りれき</t>
-  </si>
-  <si>
-    <t>りゃく</t>
-  </si>
-  <si>
-    <t>略</t>
-  </si>
-  <si>
-    <t>略図｜りゃくず
-戦略｜せんりゃく
-侵略｜しんりゃく
-侵略者｜しんりゃくしゃ</t>
   </si>
   <si>
     <t>りゅう</t>
@@ -218,6 +215,27 @@
 流行語｜りゅうこうご
 流行語大賞｜りゅうこうごたいしょう
 流通経済｜りゅうつうけいざい</t>
+  </si>
+  <si>
+    <t>りゃく</t>
+  </si>
+  <si>
+    <t>略</t>
+  </si>
+  <si>
+    <t>略図｜りゃくず
+戦略｜せんりゃく
+侵略｜しんりゃく
+侵略者｜しんりゃくしゃ</t>
+  </si>
+  <si>
+    <t>留</t>
+  </si>
+  <si>
+    <t>留学｜りゅうがく
+保留｜ほりゅう
+停留｜ていりゅう
+停留所｜ていりゅうじょ</t>
   </si>
   <si>
     <t>りょく</t>
@@ -238,28 +256,19 @@
 洞察力｜どうさつりょく</t>
   </si>
   <si>
-    <t>留</t>
-  </si>
-  <si>
-    <t>留学｜りゅうがく
-保留｜ほりゅう
-停留｜ていりゅう
-停留所｜ていりゅうじょ</t>
+    <t>りょ</t>
+  </si>
+  <si>
+    <t>旅</t>
+  </si>
+  <si>
+    <t>旅館｜りょかん</t>
   </si>
   <si>
     <t>緑</t>
   </si>
   <si>
     <t>緑茶｜りょくちゃ</t>
-  </si>
-  <si>
-    <t>りょ</t>
-  </si>
-  <si>
-    <t>旅</t>
-  </si>
-  <si>
-    <t>旅館｜りょかん</t>
   </si>
   <si>
     <t>りょう</t>
@@ -1628,7 +1637,7 @@
       <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1643,13 +1652,13 @@
         <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="93.6" customHeight="1" spans="1:7">
@@ -1657,42 +1666,42 @@
         <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" ht="72" spans="1:7">
+      <c r="G4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" ht="180" spans="1:7">
+    <row r="6" ht="144" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -1712,7 +1721,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" ht="72" spans="1:7">
+    <row r="7" ht="180" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>37</v>
       </c>
@@ -1723,90 +1732,99 @@
         <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" ht="83.4" customHeight="1" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="9" ht="36" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" ht="90" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="54" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="54" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" ht="108" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" ht="36" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1837,35 +1855,35 @@
     </row>
     <row r="2" ht="36" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" ht="85.8" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1896,112 +1914,112 @@
     </row>
     <row r="2" ht="126" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" ht="90" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" ht="90" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" ht="54" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="90" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" ht="36" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" ht="36" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:3">
@@ -2037,90 +2055,90 @@
     </row>
     <row r="2" ht="72" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" ht="144" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" ht="70.2" customHeight="1" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" ht="72" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
